--- a/src/test/resources/testingdata.xlsx
+++ b/src/test/resources/testingdata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1275e8de194d4f36/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="8_{462EB189-FD4C-41E4-BC59-C01C7903170F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D7373E6-6DAA-466A-AE0F-4066A7E515AF}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DD00660E-53F8-43E4-AD83-A096CBD56BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9618FBB1-D528-4AFA-B260-2C877701CB98}"/>
+    <workbookView xWindow="1920" yWindow="0" windowWidth="17496" windowHeight="12240" xr2:uid="{9525491A-C7F3-4C1D-8FE1-5D8BD30AE456}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Name</t>
   </si>
@@ -54,6 +54,12 @@
     <t>Credit Card Number</t>
   </si>
   <si>
+    <t>Name on Card</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vinaya </t>
+  </si>
+  <si>
     <t>45 Green Park Road</t>
   </si>
   <si>
@@ -63,59 +69,29 @@
     <t>Telangana</t>
   </si>
   <si>
-    <t>Ananya Sharma</t>
-  </si>
-  <si>
-    <t>102 Lake View Street</t>
-  </si>
-  <si>
-    <t>Bangalore</t>
-  </si>
-  <si>
-    <t>Karnataka</t>
-  </si>
-  <si>
-    <t>Rahul Reddy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vinaya </t>
-  </si>
-  <si>
-    <t>78 Jubilee Hills Main Road</t>
-  </si>
-  <si>
     <t>4539578763621486</t>
   </si>
   <si>
-    <t>4716347184862961</t>
-  </si>
-  <si>
-    <t>4485275742308327</t>
-  </si>
-  <si>
-    <t>Name on Card</t>
-  </si>
-  <si>
     <t>Vinaya</t>
-  </si>
-  <si>
-    <t>Ananya</t>
-  </si>
-  <si>
-    <t>Rahul</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -138,9 +114,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -156,10 +133,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -458,113 +431,66 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAB2F568-2543-4A99-AF4F-238666EC6569}">
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0B93428-7B0D-4C69-B3AA-A6FF2E7CD4C3}">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="19.44140625" customWidth="1"/>
-    <col min="2" max="2" width="22.6640625" customWidth="1"/>
-    <col min="3" max="3" width="15.6640625" customWidth="1"/>
-    <col min="4" max="4" width="16.88671875" customWidth="1"/>
-    <col min="5" max="5" width="15.44140625" customWidth="1"/>
-    <col min="6" max="6" width="28" customWidth="1"/>
-    <col min="7" max="7" width="16.5546875" customWidth="1"/>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="18.33203125" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" customWidth="1"/>
+    <col min="4" max="4" width="13.44140625" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" customWidth="1"/>
+    <col min="6" max="6" width="20.88671875" customWidth="1"/>
+    <col min="7" max="7" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:7">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
-        <v>19</v>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
+    <row r="2" spans="1:7">
+      <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D2" t="s">
+      <c r="B2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="1">
+      <c r="C2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="2">
         <v>500081</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="F2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D3" t="s">
+      <c r="G2" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="E3" s="1">
-        <v>560034</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="1">
-        <v>500033</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" t="s">
-        <v>22</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>